--- a/public/exports-with-coowners/29189471.xlsx
+++ b/public/exports-with-coowners/29189471.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311255644</t>
+          <t xml:space="preserve">311255646</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -8014,7 +8014,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258849</t>
+          <t xml:space="preserve">311258853</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">

--- a/public/exports-with-coowners/29189471.xlsx
+++ b/public/exports-with-coowners/29189471.xlsx
@@ -6889,7 +6889,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311255646</t>
+          <t xml:space="preserve">311255644</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -8014,7 +8014,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258853</t>
+          <t xml:space="preserve">311258849</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
